--- a/cases/the-weekly-rate/published/The Weekly Rate - Data.xlsx
+++ b/cases/the-weekly-rate/published/The Weekly Rate - Data.xlsx
@@ -852,7 +852,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Whizz Storm-1 weekly plan (NOT Dara's choice)</t>
+          <t>Whizz Storm-2 weekly plan (NOT Dara's choice)</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
